--- a/ORARI CLASSI/input_excel/Orario_per_Aule_Completo.xlsx
+++ b/ORARI CLASSI/input_excel/Orario_per_Aule_Completo.xlsx
@@ -1653,7 +1653,11 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ORGANIZZAZIONE DEL CANTIERE</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ECOLOGIA INDUSTRIALE</t>
@@ -1676,11 +1680,7 @@
           <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ORGANIZZAZIONE DEL CANTIERE</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -1804,7 +1804,11 @@
           <t>TECNICA URBANISTICA</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ORGANIZZAZIONE DEL CANTIERE</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>ECOLOGIA INDUSTRIALE</t>
@@ -1827,11 +1831,7 @@
           <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ORGANIZZAZIONE DEL CANTIERE</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -1983,7 +1983,11 @@
           <t>TECNICA URBANISTICA</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ORGANIZZAZIONE DEL CANTIERE</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>ECOLOGIA INDUSTRIALE</t>
@@ -2006,11 +2010,7 @@
           <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>ORGANIZZAZIONE DEL CANTIERE</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -2116,7 +2116,11 @@
         </is>
       </c>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>IOT SYSTEMS DESIGN</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr">
         <is>
           <t>ARCHITETTURA E COMPOSIZIONE ARCHITETTONICA I</t>
@@ -2303,7 +2307,11 @@
         </is>
       </c>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>IOT SYSTEMS DESIGN</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr">
         <is>
           <t>ARCHITETTURA E COMPOSIZIONE ARCHITETTONICA I</t>
@@ -4968,7 +4976,11 @@
           <t>PROCESSI SOSTENIBILI DELLA CHIMICA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>ADVANCED MATERIALS AND MANUFACTURING</t>
@@ -4989,11 +5001,7 @@
           <t>MECHANICAL VIBRATIONS</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -5155,7 +5163,11 @@
           <t>PROCESSI SOSTENIBILI DELLA CHIMICA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>ADVANCED MATERIALS AND MANUFACTURING</t>
@@ -5176,11 +5188,7 @@
           <t>MECHANICAL VIBRATIONS</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -5362,7 +5370,11 @@
           <t>PROCESSI SOSTENIBILI DELLA CHIMICA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>ADVANCED MATERIALS AND MANUFACTURING</t>
@@ -5370,7 +5382,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>* IOT SYSTEMS DESIGN</t>
+          <t>IOT SYSTEMS DESIGN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5385,7 +5397,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
+          <t>TECNICA URBANISTICA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -5464,11 +5476,7 @@
           <t>IMPIANTI DELL'INDUSTRIA DI PROCESSO</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>TECNICA URBANISTICA</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>CONTROLLI AUTOMATICI (A-H)</t>
@@ -5585,7 +5593,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>* IOT SYSTEMS DESIGN</t>
+          <t>IOT SYSTEMS DESIGN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5600,7 +5608,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>TECNICA URBANISTICA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -5681,7 +5689,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>TECNICA URBANISTICA</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5808,7 +5816,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>* IOT SYSTEMS DESIGN</t>
+          <t>IOT SYSTEMS DESIGN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5823,7 +5831,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>TECNICA URBANISTICA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5896,7 +5904,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>TECNICA URBANISTICA</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -6000,11 +6008,7 @@
           <t>COSTRUZIONE DI MACCHINE ED ELEMENTI FINITI</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>TERMODINAMICA E TRASMISSIONE DEL CALORE</t>
@@ -6069,7 +6073,11 @@
           <t>MODELLISTICA MATEMATICA E CONTROLLO PER L'INDUSTRIA DI PROCESSO</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
@@ -6173,7 +6181,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SYSTEM ON CHIP</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -6352,7 +6364,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SYSTEM ON CHIP</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
@@ -7175,7 +7191,11 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>VALUTAZIONE ECONOMICA DEI PROGETTI</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>* ANTENNE</t>
@@ -7187,7 +7207,11 @@
           <t>MODELLISTICA DEI SISTEMI ENERGETICI E PROPULSIVI</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FONDAZIONI</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>TECNOLOGIA MECCANICA</t>
@@ -7215,11 +7239,7 @@
           <t>SISTEMI EMBEDDED (A-H)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>FONDAZIONI</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>ARTIFICIAL INTELLIGENCE FOR CYBERSECURITY</t>
@@ -7350,7 +7370,11 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VALUTAZIONE ECONOMICA DEI PROGETTI</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>* ANTENNE</t>
@@ -7364,7 +7388,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>FONDAZIONI</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -7396,7 +7420,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>FONDAZIONI</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -7551,7 +7575,11 @@
           <t>* ANTENNE</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>MODELLISTICA DEI SISTEMI ENERGETICI E PROPULSIVI</t>
@@ -7559,7 +7587,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>FONDAZIONI</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -7591,7 +7619,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>FONDAZIONI</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -7754,11 +7782,15 @@
           <t>* BLOCKCHAINS</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>ADVANCED COMPUTATIONAL MECHANICS WITH APPLICATIONS TO COMPOSITE MATERIALS AND STRUCTURES</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -7794,7 +7826,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ADVANCED COMPUTATIONAL MECHANICS WITH APPLICATIONS TO COMPOSITE MATERIALS AND STRUCTURES</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -7957,11 +7989,15 @@
           <t>* BLOCKCHAINS</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>ADVANCED COMPUTATIONAL MECHANICS WITH APPLICATIONS TO COMPOSITE MATERIALS AND STRUCTURES</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -7997,7 +8033,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ADVANCED COMPUTATIONAL MECHANICS WITH APPLICATIONS TO COMPOSITE MATERIALS AND STRUCTURES</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -8251,11 +8287,7 @@
           <t>CARTOGRAFIA NUMERICA E GIS</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>VALUTAZIONE ECONOMICA DEI PROGETTI</t>
-        </is>
-      </c>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -8442,11 +8474,7 @@
           <t>CARTOGRAFIA NUMERICA E GIS</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>VALUTAZIONE ECONOMICA DEI PROGETTI</t>
-        </is>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr">
@@ -9333,11 +9361,7 @@
           <t>ADVANCED MATERIALS AND MANUFACTURING</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ARCHITETTURA TECNICA II</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>FISICA II</t>
@@ -9355,7 +9379,11 @@
           <t>FISICA</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ARCHITETTURA TECNICA II</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>SISTEMI EMBEDDED (I-Z)</t>
@@ -9516,11 +9544,7 @@
           <t>ADVANCED MATERIALS AND MANUFACTURING</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ARCHITETTURA TECNICA II</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>FISICA II</t>
@@ -9538,7 +9562,11 @@
           <t>FISICA</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ARCHITETTURA TECNICA II</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>SISTEMI EMBEDDED (I-Z)</t>
@@ -9688,11 +9716,7 @@
           <t>MECCATRONICA</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>* IOT SYSTEMS DESIGN</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>FIBRE OTTICHE - 6 CFU</t>
@@ -9703,11 +9727,7 @@
           <t>ECOLOGIA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ARCHITETTURA TECNICA II</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>TECNOLOGIE GENERALI DEI MATERIALI</t>
@@ -9725,7 +9745,11 @@
           <t>MATEMATICA II</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ARCHITETTURA TECNICA II</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>MACHINE LEARNING</t>
@@ -9810,11 +9834,7 @@
           <t>TRANSPORT PHENOMENA IN FOOD PROCESSES - FENOMENI DI TRASPORTO NELL'INDUSTRIA ALIMENTARE</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
-        </is>
-      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr">
         <is>
           <t>PIANIFICAZIONE DEI TRASPORTI SOSTENIBILI</t>
@@ -9871,11 +9891,7 @@
           <t>HYBRID VEHICLES</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>* IOT SYSTEMS DESIGN</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>FIBRE OTTICHE - 6 CFU</t>
@@ -9888,7 +9904,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>IMPIANTI ELETTRICI AD USO CIVILE</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -9910,7 +9926,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>IMPIANTI ELETTRICI AD USO CIVILE</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -9997,11 +10013,7 @@
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
-        </is>
-      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr">
         <is>
           <t>PIANIFICAZIONE DEI TRASPORTI SOSTENIBILI</t>
@@ -10063,7 +10075,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>IMPIANTI ELETTRICI AD USO CIVILE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -10085,7 +10097,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>IMPIANTI ELETTRICI AD USO CIVILE</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -10160,11 +10172,7 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
-        </is>
-      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr">
         <is>
           <t>PIANIFICAZIONE DEI TRASPORTI SOSTENIBILI</t>
@@ -10218,7 +10226,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SCIENZA DELLE COSTRUZIONI</t>
+          <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -10236,7 +10244,7 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
+          <t>SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -10355,7 +10363,11 @@
           <t>MECHANICAL VIBRATIONS</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>TECNOLOGIA MECCANICA</t>
@@ -10369,11 +10381,7 @@
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>ALGORITMI E PROTOCOLLI PER LA SICUREZZA (A-H)</t>
@@ -10642,11 +10650,7 @@
           <t>QUALITA' DELL'AMBIENTE INTERNO PER LA DECARBONIZZAZIONE</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SYSTEM ON CHIP</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -10781,11 +10785,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>SYSTEM ON CHIP</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>

--- a/ORARI CLASSI/input_excel/Orario_per_Aule_Completo.xlsx
+++ b/ORARI CLASSI/input_excel/Orario_per_Aule_Completo.xlsx
@@ -575,72 +575,72 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Aula Virtuale - Fisciano</t>
+          <t>Aula multimediale Lab. Strutture</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Aula multimediale Lab. Strutture</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Centro Linguistico di Ateneo</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Centro Linguistico di Ateneo</t>
+          <t>DaD</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>DaD</t>
+          <t>Didattica a distanza</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Didattica a distanza</t>
+          <t>L8PTE005</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE005</t>
+          <t>L8PTE011</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE011</t>
+          <t>L8PTE012</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE012</t>
+          <t>LINGUA INGLESE B1</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
+          <t>Lab di Ing Sanitaria</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Lab di Ing Sanitaria</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio</t>
+          <t>Laboratorio 152 - Software Matematico</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio 152 - Software Matematico</t>
+          <t>Laboratorio A4</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio A4</t>
+          <t>Laboratorio I8</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -828,32 +828,32 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>SPERIMENTAZIONE E MONITORAGGIO DELLE STRUTTURE ESISTENTI</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>SISTEMI DI MISURA IN TEMPO REALE</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>SISTEMI DI MISURA IN TEMPO REALE</t>
+          <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
           <t>LINGUA INGLESE B1</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
@@ -864,11 +864,7 @@
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
-        </is>
-      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
@@ -903,7 +899,11 @@
           <t>PROCESSI CHIMICI PER LE NANOTECNOLOGIE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CARTOGRAFIA NUMERICA E GIS</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -999,44 +999,44 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>SPERIMENTAZIONE E MONITORAGGIO DELLE STRUTTURE ESISTENTI</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+          <t>SISTEMI DI MISURA IN TEMPO REALE</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>SISTEMI DI MISURA IN TEMPO REALE</t>
+          <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
           <t>LINGUA INGLESE B1</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>PHOTOVOLTAIC BUILDING INTEGRATION AND MANAGEMENT</t>
         </is>
       </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1055,16 +1055,8 @@
           <t>INDUSTRIAL MICROBIOLOGY - MICROBIOLOGIA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>CARTOGRAFIA NUMERICA E GIS</t>
-        </is>
-      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1102,7 +1094,11 @@
           <t>PROCESSI CHIMICI PER LE NANOTECNOLOGIE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CARTOGRAFIA NUMERICA E GIS</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
@@ -1202,48 +1198,48 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>SPERIMENTAZIONE E MONITORAGGIO DELLE STRUTTURE ESISTENTI</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>SPERIMENTAZIONE E MONITORAGGIO DELLE STRUTTURE ESISTENTI</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>RIFIUTI, ENERGIA ED ECONOMIA CIRCOLARE</t>
         </is>
       </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>PHOTOVOLTAIC BUILDING INTEGRATION AND MANAGEMENT</t>
         </is>
       </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1267,11 +1263,7 @@
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>CARTOGRAFIA NUMERICA E GIS</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr">
         <is>
@@ -1305,7 +1297,11 @@
           <t>TECNOLOGIA DELLE PARTICELLE PARTICLE TECHNOLOGY</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CARTOGRAFIA NUMERICA E GIS</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
@@ -1405,41 +1401,41 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr">
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>RIFIUTI, ENERGIA ED ECONOMIA CIRCOLARE</t>
         </is>
       </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
@@ -1470,11 +1466,7 @@
           <t>IDROLOGIA</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>CARTOGRAFIA NUMERICA E GIS</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr">
@@ -1592,33 +1584,33 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr">
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
         <is>
           <t>RIFIUTI, ENERGIA ED ECONOMIA CIRCOLARE</t>
         </is>
       </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
@@ -1747,24 +1739,20 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>LABORATORIO DI ORGANIZZAZIONE E SICUREZZA DEI CANTIERI EDILI E DELLE INFRASTRUTTURE</t>
-        </is>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>MUSIC DYNAMICS</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+          <t>NANOELETTRONICA E SENSORI</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr"/>
@@ -1788,7 +1776,11 @@
           <t>DATA SCIENCE AND MACHINE LEARNING</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>LABORATORIO DI ORGANIZZAZIONE E SICUREZZA DEI CANTIERI EDILI E DELLE INFRASTRUTTURE</t>
+        </is>
+      </c>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
     </row>
@@ -1915,24 +1907,28 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
+          <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+          <t>NANOELETTRONICA E SENSORI</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>RIFIUTI, ENERGIA ED ECONOMIA CIRCOLARE</t>
         </is>
       </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
@@ -1959,13 +1955,13 @@
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>LABORATORIO DI ORGANIZZAZIONE E SICUREZZA DEI CANTIERI EDILI E DELLE INFRASTRUTTURE</t>
+        </is>
+      </c>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>LABORATORIO DI ORGANIZZAZIONE E SICUREZZA DEI CANTIERI EDILI E DELLE INFRASTRUTTURE</t>
-        </is>
-      </c>
+      <c r="BE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2004,7 +2000,11 @@
           <t>* CLOUD SYSTEMS AND ADVANCED NETWORKING</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MONITORAGGIO GEOMATICO</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>SUSTAINABILITY AND SAFETY IN SMART INDUSTRIAL PROCESSES</t>
@@ -2090,31 +2090,35 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
+          <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+          <t>NANOELETTRONICA E SENSORI</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>RIFIUTI, ENERGIA ED ECONOMIA CIRCOLARE</t>
         </is>
       </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>LABORATORIO DI PROGETTAZIONE EDILIZIA E TECNOLOGICA</t>
         </is>
       </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
@@ -2133,11 +2137,7 @@
           <t>MANAGING INNOVATION IN THE FOOD INDUSTRY GESTIONE DELL'INNOVAZIONE NELL'INDUSTRIA ALIMENTARE</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>MONITORAGGIO GEOMATICO</t>
-        </is>
-      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr">
         <is>
           <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
@@ -2150,13 +2150,13 @@
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>LABORATORIO DI ORGANIZZAZIONE E SICUREZZA DEI CANTIERI EDILI E DELLE INFRASTRUTTURE</t>
+        </is>
+      </c>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>LABORATORIO DI ORGANIZZAZIONE E SICUREZZA DEI CANTIERI EDILI E DELLE INFRASTRUTTURE</t>
-        </is>
-      </c>
+      <c r="BE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2195,7 +2195,11 @@
           <t>* CLOUD SYSTEMS AND ADVANCED NETWORKING</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MONITORAGGIO GEOMATICO</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
@@ -2277,35 +2281,31 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
-        </is>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>TECNICHE PER IL CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
         </is>
       </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>LABORATORIO DI PROGETTAZIONE EDILIZIA E TECNOLOGICA</t>
         </is>
       </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
@@ -2328,11 +2328,7 @@
           <t>MANAGING INNOVATION IN THE FOOD INDUSTRY GESTIONE DELL'INNOVAZIONE NELL'INDUSTRIA ALIMENTARE</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>MONITORAGGIO GEOMATICO</t>
-        </is>
-      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr">
         <is>
           <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
@@ -2382,7 +2378,11 @@
           <t>* CLOUD SYSTEMS AND ADVANCED NETWORKING</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MONITORAGGIO GEOMATICO</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
@@ -2460,35 +2460,31 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
-        </is>
-      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>TECNICHE PER IL CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
         </is>
       </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>LABORATORIO DI PROGETTAZIONE EDILIZIA E TECNOLOGICA</t>
         </is>
       </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
@@ -2499,11 +2495,7 @@
       </c>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>MONITORAGGIO GEOMATICO</t>
-        </is>
-      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr">
         <is>
           <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
@@ -2673,72 +2665,72 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Aula Virtuale - Fisciano</t>
+          <t>Aula multimediale Lab. Strutture</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Aula multimediale Lab. Strutture</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Centro Linguistico di Ateneo</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Centro Linguistico di Ateneo</t>
+          <t>DaD</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>DaD</t>
+          <t>Didattica a distanza</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Didattica a distanza</t>
+          <t>L8PTE005</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE005</t>
+          <t>L8PTE011</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE011</t>
+          <t>L8PTE012</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE012</t>
+          <t>LINGUA INGLESE B1</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
+          <t>Lab di Ing Sanitaria</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Lab di Ing Sanitaria</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio</t>
+          <t>Laboratorio 152 - Software Matematico</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio 152 - Software Matematico</t>
+          <t>Laboratorio A4</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio A4</t>
+          <t>Laboratorio I8</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -2845,8 +2837,16 @@
           <t>* TECNOLOGIE ELETTRICHE PER L'INFORMATICA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>IDROLOGIA</t>
@@ -2939,22 +2939,22 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>MISURE BASATE SU VISIONE</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>MISURE BASATE SU VISIONE</t>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
@@ -2974,17 +2974,13 @@
           <t>COMBUSTIONE</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -3013,7 +3009,11 @@
           <t>COMBUSTIONE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>MECCATRONICA</t>
@@ -3024,8 +3024,16 @@
           <t>* TECNOLOGIE ELETTRICHE PER L'INFORMATICA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>IDROLOGIA</t>
@@ -3122,22 +3130,22 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>MISURE BASATE SU VISIONE</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>MISURE BASATE SU VISIONE</t>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
@@ -3163,19 +3171,11 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
-        </is>
-      </c>
+          <t>GESTIONE E RIQUALIFICAZIONE DELLE COSTRUZIONI IDRAULICHE</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -3208,7 +3208,11 @@
           <t>IMPIANTI CHIMICI INNOVATIVI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>IMPIANTI DI CONDIZIONAMENTO</t>
@@ -3219,8 +3223,16 @@
           <t>* BLOCKCHAINS</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>IDROLOGIA</t>
@@ -3313,22 +3325,22 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>MISURE BASATE SU VISIONE</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>MISURE BASATE SU VISIONE</t>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
@@ -3348,21 +3360,9 @@
           <t>IMPIANTI DELL'INDUSTRIA ALIMENTARE I</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>OPERATIONS AND MAINTENANCE MANAGEMENT IN SMART MANUFACTURING SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -3395,7 +3395,11 @@
           <t>IMPIANTI CHIMICI INNOVATIVI</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>IMPIANTI DI CONDIZIONAMENTO</t>
@@ -3406,7 +3410,11 @@
           <t>* BLOCKCHAINS</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>MECHANICAL VIBRATIONS</t>
@@ -3499,12 +3507,12 @@
           <t>CIRCUITI E SISTEMI DIGITALI (I-Z)</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>TECNICA DELLE COSTRUZIONI E GEOTECNICA</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -3514,12 +3522,12 @@
           <t>NANOELETTRONICA E SENSORI</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
@@ -3535,11 +3543,7 @@
           <t>IMPIANTI DELL'INDUSTRIA ALIMENTARE I</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
-        </is>
-      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr">
         <is>
           <t>ECOLOGIA APPLICATA</t>
@@ -3589,7 +3593,11 @@
           <t>* BLOCKCHAINS</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>MECHANICAL VIBRATIONS</t>
@@ -3639,11 +3647,7 @@
           <t>MECCANICA RAZIONALE E SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
-        </is>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>ARCHITETTURA TECNICA II</t>
@@ -3670,12 +3674,12 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>TECNICA DELLE COSTRUZIONI E GEOTECNICA</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -3685,21 +3689,21 @@
           <t>NANOELETTRONICA E SENSORI</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>MULTIPHYSICS MODELS FOR ELECTRICAL SYSTEM VIRTUALIZATION</t>
         </is>
       </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
@@ -3757,7 +3761,11 @@
           <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
@@ -3814,11 +3822,7 @@
           <t>MECCANICA RAZIONALE E SCIENZA DELLE COSTRUZIONI</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>ARCHITETTURA TECNICA II</t>
@@ -3837,40 +3841,44 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>MONITORAGGIO E ISPEZIONE DELLE OPERE D'ARTE STRADALI</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
+          <t>NANOELETTRONICA E SENSORI</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
+        </is>
+      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
           <t>TECNICHE DI REALIZZAZIONE E CARATTERIZZAZIONE DI STRATI SOTTILI</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>MULTIPHYSICS MODELS FOR ELECTRICAL SYSTEM VIRTUALIZATION</t>
         </is>
       </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
@@ -3885,21 +3893,13 @@
           <t>ADVANCED TECHNOLOGIES FOR FOOD PACKAGING TECNOLOGIE AVANZATE PER I MATERIALI PER IMBALLAGGI</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
-        </is>
-      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr">
         <is>
           <t>ECOLOGIA APPLICATA</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>ELECTROMAGNETIC COMPATIBILITY</t>
-        </is>
-      </c>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
@@ -3936,7 +3936,11 @@
           <t>SOSTENIBILITÀ ENERGETICA ED AMBIENTALE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
@@ -4028,34 +4032,34 @@
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>MONITORAGGIO E ISPEZIONE DELLE OPERE D'ARTE STRADALI</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>MUSIC DYNAMICS</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
+        </is>
+      </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
           <t>TECNICHE DI REALIZZAZIONE E CARATTERIZZAZIONE DI STRATI SOTTILI</t>
         </is>
       </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
@@ -4076,28 +4080,24 @@
           <t>ADVANCED TECHNOLOGIES FOR FOOD PACKAGING TECNOLOGIE AVANZATE PER I MATERIALI PER IMBALLAGGI</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
-        </is>
-      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr">
         <is>
           <t>LABORATORIO DI MODELLAZIONE DEI PROCESSI AMBIENTALI</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>ELECTROMAGNETIC COMPATIBILITY</t>
-        </is>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr">
         <is>
           <t>PHOTOVOLTAIC BUILDING INTEGRATION AND MANAGEMENT</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>ELECTROMAGNETIC COMPATIBILITY</t>
+        </is>
+      </c>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4231,40 +4231,40 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>TEORIA DELLE STRUTTURE</t>
         </is>
       </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>MUSIC DYNAMICS</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>* CYBERSECURITY APPLICATIONS</t>
+        </is>
+      </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>* CYBERSECURITY APPLICATIONS</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
           <t>LABORATORIO DI INFORMATICA GRAFICA E BIM</t>
         </is>
       </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4434,17 +4434,17 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TEORIA DELLE STRUTTURE</t>
+        </is>
+      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>TEORIA DELLE STRUTTURE</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
@@ -4453,17 +4453,17 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>* CYBERSECURITY APPLICATIONS</t>
+        </is>
+      </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>* CYBERSECURITY APPLICATIONS</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
           <t>LABORATORIO DI INFORMATICA GRAFICA E BIM</t>
         </is>
       </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4609,17 +4609,17 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TEORIA DELLE STRUTTURE</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>TEORIA DELLE STRUTTURE</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
@@ -4629,12 +4629,12 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>LABORATORIO DI INFORMATICA GRAFICA E BIM</t>
         </is>
       </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4811,72 +4811,72 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Aula Virtuale - Fisciano</t>
+          <t>Aula multimediale Lab. Strutture</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Aula multimediale Lab. Strutture</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Centro Linguistico di Ateneo</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Centro Linguistico di Ateneo</t>
+          <t>DaD</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>DaD</t>
+          <t>Didattica a distanza</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Didattica a distanza</t>
+          <t>L8PTE005</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE005</t>
+          <t>L8PTE011</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE011</t>
+          <t>L8PTE012</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE012</t>
+          <t>LINGUA INGLESE B1</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
+          <t>Lab di Ing Sanitaria</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Lab di Ing Sanitaria</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio</t>
+          <t>Laboratorio 152 - Software Matematico</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio 152 - Software Matematico</t>
+          <t>Laboratorio A4</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio A4</t>
+          <t>Laboratorio I8</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -5001,7 +5001,11 @@
           <t>MECHANICAL VIBRATIONS</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VIRTUAL DESIGN FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -5085,19 +5089,19 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>RETI E PROTOCOLLI PER LA  INTERNET OF THINGS</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>LINGUA INGLESE B1</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
@@ -5126,11 +5130,7 @@
           <t>LABORATORIO DI MODELLAZIONE DEI PROCESSI AMBIENTALI</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>VIRTUAL DESIGN FOR SMART INDUSTRY</t>
-        </is>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -5188,7 +5188,11 @@
           <t>MECHANICAL VIBRATIONS</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VIRTUAL DESIGN FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>MECCANICA APPLICATA ALLE MACCHINE</t>
@@ -5271,40 +5275,40 @@
           <t>RETI DI CALCOLATORI (A-H)</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>ISOLAMENTO SISMICO ALLA BASE E DISSIPAZIONE</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>RETI E PROTOCOLLI PER LA  INTERNET OF THINGS</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>LINGUA INGLESE B1</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr">
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>TECNICHE DI REALIZZAZIONE E CARATTERIZZAZIONE DI STRATI SOTTILI</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>DATA SCIENCE AND MACHINE LEARNING</t>
         </is>
       </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
         <is>
           <t>MANAGING INNOVATION IN THE FOOD INDUSTRY GESTIONE DELL'INNOVAZIONE NELL'INDUSTRIA ALIMENTARE</t>
@@ -5329,11 +5333,7 @@
           <t>LABORATORIO DI MODELLAZIONE DEI PROCESSI AMBIENTALI</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>VIRTUAL DESIGN FOR SMART INDUSTRY</t>
-        </is>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -5482,44 +5482,40 @@
           <t>CONTROLLI AUTOMATICI (A-H)</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>ISOLAMENTO SISMICO ALLA BASE E DISSIPAZIONE</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>ISOLAMENTO SISMICO ALLA BASE E DISSIPAZIONE</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>NANOELETTRONICA E SENSORI</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
           <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>TECNICHE DI REALIZZAZIONE E CARATTERIZZAZIONE DI STRATI SOTTILI</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>DATA SCIENCE AND MACHINE LEARNING</t>
         </is>
       </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
@@ -5697,48 +5693,44 @@
           <t>CONTROLLI AUTOMATICI (A-H)</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ISOLAMENTO SISMICO ALLA BASE E DISSIPAZIONE</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>ISOLAMENTO SISMICO ALLA BASE E DISSIPAZIONE</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
           <t>INGLESE</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NANOELETTRONICA E SENSORI</t>
+          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>CIRCUITI ELETTRONICI DI POTENZA</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>TECNICHE DI REALIZZAZIONE E CARATTERIZZAZIONE DI STRATI SOTTILI</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>MULTIPHYSICS MODELS FOR ELECTRICAL SYSTEM VIRTUALIZATION</t>
         </is>
       </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
@@ -5908,36 +5900,32 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>PROGETTO DI EDIFICI IN ZONA SISMICA</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>NANOELETTRONICA E SENSORI</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>RETI DI CALCOLATORI</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>MULTIPHYSICS MODELS FOR ELECTRICAL SYSTEM VIRTUALIZATION</t>
         </is>
       </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
@@ -5995,13 +5983,21 @@
           <t>SICUREZZA E PROTEZIONE AMBIENTALE DEI PROCESSI CHIMICI</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TECHNOLOGIES AND METHODS FOR ENERGY MANAGEMENT IN SMART INDUSTRIES</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>SISTEMI DI MISURA PER L'INDUSTRIA 4.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -6079,36 +6075,40 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>PROGETTO DI EDIFICI IN ZONA SISMICA</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>MULTIPHYSICS MODELS FOR ELECTRICAL SYSTEM VIRTUALIZATION</t>
         </is>
       </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr">
         <is>
@@ -6123,21 +6123,13 @@
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
-        </is>
-      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr">
         <is>
           <t>FOOD PACKAGING - MATERIALI PER IMBALLAGGI</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>TECHNOLOGIES AND METHODS FOR ENERGY MANAGEMENT IN SMART INDUSTRIES</t>
-        </is>
-      </c>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr">
@@ -6174,13 +6166,21 @@
           <t>SICUREZZA E PROTEZIONE AMBIENTALE DEI PROCESSI CHIMICI</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TECHNOLOGIES AND METHODS FOR ENERGY MANAGEMENT IN SMART INDUSTRIES</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>SISTEMI DI MISURA PER L'INDUSTRIA 4.0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>SYSTEM ON CHIP</t>
@@ -6274,27 +6274,31 @@
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>PROGETTO DI EDIFICI IN ZONA SISMICA</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
@@ -6314,21 +6318,13 @@
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
-        </is>
-      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr">
         <is>
           <t>IMPIANTI ELETTRICI AD USO CIVILE</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>TECHNOLOGIES AND METHODS FOR ENERGY MANAGEMENT IN SMART INDUSTRIES</t>
-        </is>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -6361,9 +6357,17 @@
           <t>INGEGNERIA CHIMICA AMBIENTALE</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TECHNOLOGIES AND METHODS FOR ENERGY MANAGEMENT IN SMART INDUSTRIES</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>SYSTEM ON CHIP</t>
@@ -6458,18 +6462,22 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
@@ -6489,21 +6497,13 @@
           <t>TRANSPORT PHENOMENA IN FOOD PROCESSES - FENOMENI DI TRASPORTO NELL'INDUSTRIA ALIMENTARE</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>MIGLIORAMENTO SISMICO DEGLI EDIFICI</t>
-        </is>
-      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr">
         <is>
           <t>IMPIANTI ELETTRICI AD USO CIVILE</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>TECHNOLOGIES AND METHODS FOR ENERGY MANAGEMENT IN SMART INDUSTRIES</t>
-        </is>
-      </c>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr">
         <is>
           <t>FONDAMENTI DI MISURE E STRUMENTAZIONE VIRTUALE</t>
@@ -6536,7 +6536,11 @@
           <t>INGEGNERIA CHIMICA AMBIENTALE</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ELECTRIC MACHINES AND DRIVES FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>VIBROACUSTICA COMPUTAZIONALE</t>
@@ -6634,34 +6638,30 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>LINGUA INGLESE B1</t>
-        </is>
-      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>MUSIC DYNAMICS</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>MUSIC DYNAMICS</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
           <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>LABORATORIO DI PROGETTAZIONE EDILIZIA E TECNOLOGICA</t>
         </is>
       </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
@@ -6719,7 +6719,11 @@
           <t>INGEGNERIA CHIMICA AMBIENTALE</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ELECTRIC MACHINES AND DRIVES FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>VIBROACUSTICA COMPUTAZIONALE</t>
@@ -6813,30 +6817,26 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>LINGUA INGLESE B1</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>CIRCUITI ELETTRONICI DI POTENZA</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>LABORATORIO DI PROGETTAZIONE EDILIZIA E TECNOLOGICA</t>
         </is>
       </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
@@ -7025,72 +7025,72 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Aula Virtuale - Fisciano</t>
+          <t>Aula multimediale Lab. Strutture</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Aula multimediale Lab. Strutture</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Centro Linguistico di Ateneo</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Centro Linguistico di Ateneo</t>
+          <t>DaD</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>DaD</t>
+          <t>Didattica a distanza</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Didattica a distanza</t>
+          <t>L8PTE005</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE005</t>
+          <t>L8PTE011</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE011</t>
+          <t>L8PTE012</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE012</t>
+          <t>LINGUA INGLESE B1</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
+          <t>Lab di Ing Sanitaria</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Lab di Ing Sanitaria</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio</t>
+          <t>Laboratorio 152 - Software Matematico</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio 152 - Software Matematico</t>
+          <t>Laboratorio A4</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio A4</t>
+          <t>Laboratorio I8</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -7190,7 +7190,11 @@
           <t>IMPIANTI DELL'INDUSTRIA ALIMENTARE I</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>VALUTAZIONE ECONOMICA DEI PROGETTI</t>
@@ -7201,7 +7205,11 @@
           <t>* ANTENNE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SOSTENIBILITÀ DEI SISTEMI IDRICI</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>MODELLISTICA DEI SISTEMI ENERGETICI E PROPULSIVI</t>
@@ -7295,26 +7303,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>RETI E PROTOCOLLI PER LA  INTERNET OF THINGS</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>* TECNOLOGIE ELETTRICHE PER L'INFORMATICA INDUSTRIALE</t>
         </is>
       </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
@@ -7327,16 +7335,8 @@
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SOSTENIBILITÀ DEI SISTEMI IDRICI</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
@@ -7369,7 +7369,11 @@
           <t>IMPIANTI DELL'INDUSTRIA ALIMENTARE I</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>VALUTAZIONE ECONOMICA DEI PROGETTI</t>
@@ -7380,7 +7384,11 @@
           <t>* ANTENNE</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SOSTENIBILITÀ DEI SISTEMI IDRICI</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>MODELLISTICA DEI SISTEMI ENERGETICI E PROPULSIVI</t>
@@ -7478,26 +7486,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>RETI E PROTOCOLLI PER LA  INTERNET OF THINGS</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>* TECNOLOGIE ELETTRICHE PER L'INFORMATICA INDUSTRIALE</t>
         </is>
       </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
@@ -7513,21 +7521,13 @@
           <t>TRANSPORT PHENOMENA IN FOOD PROCESSES - FENOMENI DI TRASPORTO NELL'INDUSTRIA ALIMENTARE</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SOSTENIBILITÀ DEI SISTEMI IDRICI</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
@@ -7564,7 +7564,11 @@
           <t>IMPIANTI DELL'INDUSTRIA ALIMENTARE I</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>SCIENZA DELLE COSTRUZIONI</t>
@@ -7672,39 +7676,39 @@
           <t>SISTEMI OPERATIVI (I-Z)</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>RETI E PROTOCOLLI PER LA  INTERNET OF THINGS</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>* TECNOLOGIE ELETTRICHE PER L'INFORMATICA INDUSTRIALE</t>
         </is>
       </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
@@ -7722,19 +7726,15 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>TECNICA DELLE COSTRUZIONI ED ELEMENTI DI INGEGNERIA SISMICA</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
           <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>TECNICA DELLE COSTRUZIONI ED ELEMENTI DI INGEGNERIA SISMICA</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
@@ -7771,7 +7771,11 @@
           <t>IMPIANTI CHIMICI INNOVATIVI</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TECNICA DELLE COSTRUZIONI E GEOTECNICA</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>SCIENZA DELLE COSTRUZIONI</t>
@@ -7879,33 +7883,37 @@
           <t>SISTEMI OPERATIVI (I-Z)</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>SISTEMI COSTRUTTIVI SOSTENIBILI E ANALISI DEL CICLO DI VITA</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr">
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>TRATTAMENTO ACQUE E RIUTILIZZO</t>
         </is>
       </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
@@ -7929,19 +7937,15 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>TECNICA DELLE COSTRUZIONI ED ELEMENTI DI INGEGNERIA SISMICA</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
           <t>LABORATORIO PROGETTUALE IN UN CONTESTO MULTIRISCHIO</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>TECNICA DELLE COSTRUZIONI ED ELEMENTI DI INGEGNERIA SISMICA</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>TECNICA DELLE COSTRUZIONI E GEOTECNICA</t>
-        </is>
-      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -7978,7 +7982,11 @@
           <t>IMPIANTI CHIMICI INNOVATIVI</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TECNICA DELLE COSTRUZIONI E GEOTECNICA</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>SCIENZA DELLE COSTRUZIONI</t>
@@ -8083,18 +8091,22 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
@@ -8118,17 +8130,13 @@
           <t>PROCESSI CHIMICI PER LE NANOTECNOLOGIE</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>TECNICA DELLE COSTRUZIONI ED ELEMENTI DI INGEGNERIA SISMICA</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>TECNICA DELLE COSTRUZIONI E GEOTECNICA</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -8149,7 +8157,11 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RIVER RESTORATION</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
@@ -8233,39 +8245,39 @@
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>TEORIA DELLE STRUTTURE</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+          <t>SISTEMI DI MISURA IN TEMPO REALE</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>SISTEMI DI MISURA IN TEMPO REALE</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>DIGITAL MEDICINE APPLICATIONS</t>
         </is>
       </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
@@ -8277,11 +8289,7 @@
           <t>INDUSTRIAL MICROBIOLOGY - MICROBIOLOGIA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>RIVER RESTORATION</t>
-        </is>
-      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr">
         <is>
           <t>CARTOGRAFIA NUMERICA E GIS</t>
@@ -8312,7 +8320,11 @@
           <t>COMBUSTIONE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RIVER RESTORATION</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
@@ -8420,31 +8432,31 @@
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>TEORIA DELLE STRUTTURE</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>SISTEMI DI MISURA IN TEMPO REALE</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>DIGITAL MEDICINE APPLICATIONS</t>
         </is>
       </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr">
@@ -8464,11 +8476,7 @@
           <t>INDUSTRIAL MICROBIOLOGY - MICROBIOLOGIA INDUSTRIALE</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>RIVER RESTORATION</t>
-        </is>
-      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr">
         <is>
           <t>CARTOGRAFIA NUMERICA E GIS</t>
@@ -8511,7 +8519,11 @@
           <t>COMBUSTIONE</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>RIVER RESTORATION</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>ELETTROTECNICA APPLICATA</t>
@@ -8611,28 +8623,32 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>RINFORZO STRUTTURALE CON MATERIALI COMPOSITI</t>
         </is>
       </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>SISTEMI DI MISURA IN TEMPO REALE</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>ELECTRIC MACHINES AND DRIVES FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
@@ -8651,11 +8667,7 @@
           <t>FOOD PACKAGING - MATERIALI PER IMBALLAGGI</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>RIVER RESTORATION</t>
-        </is>
-      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
@@ -8794,32 +8806,40 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>RINFORZO STRUTTURALE CON MATERIALI COMPOSITI</t>
+        </is>
+      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>RINFORZO STRUTTURALE CON MATERIALI COMPOSITI</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr">
+          <t>LINGUA INGLESE B1</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>LINGUA INGLESE LIVELLO CEFR B1</t>
         </is>
       </c>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>MISURE BASATE SU VISIONE</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>ELECTRIC MACHINES AND DRIVES FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
@@ -8965,32 +8985,40 @@
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>RINFORZO STRUTTURALE CON MATERIALI COMPOSITI</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>RINFORZO STRUTTURALE CON MATERIALI COMPOSITI</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr">
+          <t>LINGUA INGLESE B1</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>LINGUA INGLESE LIVELLO CEFR B1</t>
         </is>
       </c>
+      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>MISURE BASATE SU VISIONE</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>ELECTRIC MACHINES AND DRIVES FOR SMART INDUSTRY</t>
+        </is>
+      </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr">
         <is>
@@ -9175,72 +9203,72 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Aula Virtuale - Fisciano</t>
+          <t>Aula multimediale Lab. Strutture</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Aula multimediale Lab. Strutture</t>
+          <t>CLA</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>CLA</t>
+          <t>Centro Linguistico di Ateneo</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Centro Linguistico di Ateneo</t>
+          <t>DaD</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>DaD</t>
+          <t>Didattica a distanza</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Didattica a distanza</t>
+          <t>L8PTE005</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE005</t>
+          <t>L8PTE011</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE011</t>
+          <t>L8PTE012</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>L8PTE012</t>
+          <t>LINGUA INGLESE B1</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
+          <t>Lab di Ing Sanitaria</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Lab di Ing Sanitaria</t>
+          <t>Laboratorio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio</t>
+          <t>Laboratorio 152 - Software Matematico</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio 152 - Software Matematico</t>
+          <t>Laboratorio A4</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Laboratorio A4</t>
+          <t>Laboratorio I8</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -9436,31 +9464,35 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>COMPLEMENTI DI TECNICA DELLE COSTRUZIONI</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>LINGUA INGLESE B1</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
           <t>LINGUA INGLESE LIVELLO CEFR B1</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
@@ -9482,11 +9514,7 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
-        </is>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr">
@@ -9619,31 +9647,35 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>COMPLEMENTI DI TECNICA DELLE COSTRUZIONI</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>LINGUA INGLESE B1</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>LINGUA INGLESE B1</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
           <t>LINGUA INGLESE LIVELLO CEFR B1</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
@@ -9665,11 +9697,7 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
-        </is>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr">
@@ -9802,23 +9830,27 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>FONDAMENTI DI PROGETTAZIONE STRUTTURALE</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>STRUMENTAZIONE VIRTUALE PER L'ACQUISIZIONE DEI SEGNALI</t>
         </is>
       </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
@@ -9840,11 +9872,7 @@
           <t>PIANIFICAZIONE DEI TRASPORTI SOSTENIBILI</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>COMPUTER SCIENCE FOR INDUSTRY 4.0: NETWORKING, BIG DATA MANAGEMENT AND MACHINE LEARNING</t>
-        </is>
-      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr">
@@ -9981,27 +10009,31 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>FONDAMENTI DI PROGETTAZIONE STRUTTURALE</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
@@ -10019,11 +10051,7 @@
           <t>PIANIFICAZIONE DEI TRASPORTI SOSTENIBILI</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
@@ -10140,27 +10168,31 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>FONDAMENTI DI PROGETTAZIONE STRUTTURALE</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>TECNOLOGIE INFORMATICHE PER LE PRODUZIONI MUSICALI</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>CONVERTITORI ELETTRONICI PER L'ENERGIA ED I TRASPORTI</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
@@ -10178,11 +10210,7 @@
           <t>PIANIFICAZIONE DEI TRASPORTI SOSTENIBILI</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -10218,7 +10246,11 @@
           <t>SYSTEM SAFETY ENGINEERING</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FENOMENI DI INQUINAMENTO E CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>MECHANICAL VIBRATIONS</t>
@@ -10289,12 +10321,12 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
-        </is>
-      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
@@ -10312,16 +10344,8 @@
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>FENOMENI DI INQUINAMENTO E CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>OPTIMIZATION AND MANAGEMENT OF ENERGY SYSTEMS</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
@@ -10357,7 +10381,11 @@
           <t>SYSTEM SAFETY ENGINEERING</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FENOMENI DI INQUINAMENTO E CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>MECHANICAL VIBRATIONS</t>
@@ -10433,21 +10461,17 @@
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>COMPLEMENTI DI ELETTROMAGNETISMO</t>
-        </is>
-      </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>LABORATORIO DI INFORMATICA GRAFICA E BIM</t>
         </is>
       </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr">
         <is>
@@ -10459,11 +10483,7 @@
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>FENOMENI DI INQUINAMENTO E CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -10508,7 +10528,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FENOMENI DI INQUINAMENTO E CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>MODELLISTICA DEI SISTEMI ENERGETICI E PROPULSIVI</t>
@@ -10579,22 +10603,22 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>LABORATORIO DI INFORMATICA GRAFICA E BIM</t>
         </is>
       </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
@@ -10606,16 +10630,8 @@
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>FENOMENI DI INQUINAMENTO E CONTROLLO DELLA QUALITÀ AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>ELECTROMAGNETIC COMPATIBILITY</t>
-        </is>
-      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr">
@@ -10651,7 +10667,11 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>MODELLISTICA DEI SISTEMI ENERGETICI E PROPULSIVI</t>
@@ -10726,12 +10746,12 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
@@ -10749,19 +10769,15 @@
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>ELECTROMAGNETIC COMPATIBILITY</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>ELECTROMAGNETIC COMPATIBILITY</t>
+        </is>
+      </c>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
     </row>
@@ -10786,7 +10802,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -10849,12 +10869,12 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>SMART ENERGY MANAGEMENT  and  TECHNOLOGIES FOR SUSTAINABILITY</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
@@ -10872,19 +10892,15 @@
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>ECONOMIA ED ESTIMO AMBIENTALE</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>ELECTROMAGNETIC COMPATIBILITY</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>ELECTROMAGNETIC COMPATIBILITY</t>
+        </is>
+      </c>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
     </row>
